--- a/docassemble/StudentEvaluations/data/sources/massachusetts_entire_student_record_request_zh-Hans_rev1.xlsx
+++ b/docassemble/StudentEvaluations/data/sources/massachusetts_entire_student_record_request_zh-Hans_rev1.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
@@ -6295,7 +6295,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
@@ -7945,7 +7945,7 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -9117,7 +9117,7 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -9317,7 +9317,7 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -9879,7 +9879,7 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -10039,7 +10039,7 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
@@ -10205,7 +10205,7 @@
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -10718,7 +10718,7 @@
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
@@ -10846,7 +10846,7 @@
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -10972,7 +10972,7 @@
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -11154,7 +11154,7 @@
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -11297,7 +11297,7 @@
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="F247" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="F251" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="F253" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -11790,7 +11790,7 @@
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="F255" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="F259" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="F261" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="F265" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -12304,7 +12304,7 @@
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="F267" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -12476,7 +12476,7 @@
       </c>
       <c r="F270" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="F271" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
@@ -12696,7 +12696,7 @@
       </c>
       <c r="F275" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="F276" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="F277" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
@@ -12818,7 +12818,7 @@
       </c>
       <c r="F278" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -12860,7 +12860,7 @@
       </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="F281" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="F283" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="F284" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="F285" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -13154,7 +13154,7 @@
       </c>
       <c r="F286" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="F287" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="F288" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="F289" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -13322,7 +13322,7 @@
       </c>
       <c r="F290" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -13362,7 +13362,7 @@
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G291" s="4" t="inlineStr">
@@ -13402,7 +13402,7 @@
       </c>
       <c r="F292" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="F293" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="F294" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="F295" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -13578,7 +13578,7 @@
       </c>
       <c r="F296" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="F297" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G297" s="3" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="F298" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
@@ -13708,7 +13708,7 @@
       </c>
       <c r="F299" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
@@ -13748,7 +13748,7 @@
       </c>
       <c r="F300" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="F301" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="F303" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
@@ -13910,7 +13910,7 @@
       </c>
       <c r="F304" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G304" s="3" t="inlineStr">
@@ -13950,7 +13950,7 @@
       </c>
       <c r="F305" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G305" s="3" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="F306" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G306" s="3" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="F307" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G307" s="3" t="inlineStr">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="F308" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G308" s="3" t="inlineStr">
@@ -14112,7 +14112,7 @@
       </c>
       <c r="F309" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G309" s="3" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="F310" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G310" s="3" t="inlineStr">
@@ -14194,7 +14194,7 @@
       </c>
       <c r="F311" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G311" s="3" t="inlineStr">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="F312" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G312" s="3" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="F313" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G313" s="3" t="inlineStr">
@@ -14316,7 +14316,7 @@
       </c>
       <c r="F314" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G314" s="3" t="inlineStr">
@@ -14378,7 +14378,7 @@
       </c>
       <c r="F315" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G315" s="3" t="inlineStr">
@@ -14420,7 +14420,7 @@
       </c>
       <c r="F316" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G316" s="3" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="F317" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G317" s="3" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="F318" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G318" s="3" t="inlineStr">
@@ -14562,7 +14562,7 @@
       </c>
       <c r="F319" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G319" s="3" t="inlineStr">
@@ -14602,7 +14602,7 @@
       </c>
       <c r="F320" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G320" s="3" t="inlineStr">
@@ -14642,7 +14642,7 @@
       </c>
       <c r="F321" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G321" s="3" t="inlineStr">
@@ -14682,7 +14682,7 @@
       </c>
       <c r="F322" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G322" s="3" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="F323" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G323" s="3" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="F324" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G324" s="3" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="F325" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G325" s="3" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="F326" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G326" s="3" t="inlineStr">
@@ -14892,7 +14892,7 @@
       </c>
       <c r="F327" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G327" s="3" t="inlineStr">
@@ -14934,7 +14934,7 @@
       </c>
       <c r="F328" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G328" s="3" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="F329" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G329" s="3" t="inlineStr">
@@ -15016,7 +15016,7 @@
       </c>
       <c r="F330" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="F331" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G331" s="3" t="inlineStr">
@@ -15096,7 +15096,7 @@
       </c>
       <c r="F332" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G332" s="3" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="F333" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G333" s="3" t="inlineStr">
@@ -15186,7 +15186,7 @@
       </c>
       <c r="F334" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G334" s="3" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="F335" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G335" s="3" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="F336" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G336" s="3" t="inlineStr">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="F337" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G337" s="3" t="inlineStr">
@@ -15389,7 +15389,7 @@
       </c>
       <c r="F338" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G338" s="3" t="inlineStr">
@@ -15429,7 +15429,7 @@
       </c>
       <c r="F339" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G339" s="4" t="inlineStr">
@@ -15469,7 +15469,7 @@
       </c>
       <c r="F340" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G340" s="3" t="inlineStr">
@@ -15511,7 +15511,7 @@
       </c>
       <c r="F341" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G341" s="3" t="inlineStr">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="F342" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G342" s="3" t="inlineStr">
@@ -15601,7 +15601,7 @@
       </c>
       <c r="F343" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G343" s="3" t="inlineStr">
@@ -15643,7 +15643,7 @@
       </c>
       <c r="F344" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G344" s="3" t="inlineStr">
@@ -15687,7 +15687,7 @@
       </c>
       <c r="F345" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G345" s="3" t="inlineStr">
@@ -15733,7 +15733,7 @@
       </c>
       <c r="F346" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G346" s="3" t="inlineStr">
@@ -15775,7 +15775,7 @@
       </c>
       <c r="F347" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G347" s="3" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="F348" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G348" s="3" t="inlineStr">
@@ -15871,7 +15871,7 @@
       </c>
       <c r="F349" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G349" s="3" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="F350" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G350" s="3" t="inlineStr">
@@ -15967,7 +15967,7 @@
       </c>
       <c r="F351" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G351" s="3" t="inlineStr">
@@ -16007,7 +16007,7 @@
       </c>
       <c r="F352" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G352" s="3" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="F353" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G353" s="3" t="inlineStr">
@@ -16120,7 +16120,7 @@
       </c>
       <c r="F354" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G354" s="3" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="F355" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G355" s="4" t="inlineStr">
@@ -16200,7 +16200,7 @@
       </c>
       <c r="F356" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="F357" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G357" s="3" t="inlineStr">
@@ -16290,7 +16290,7 @@
       </c>
       <c r="F358" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G358" s="3" t="inlineStr">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="F359" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G359" s="3" t="inlineStr">
@@ -16426,7 +16426,7 @@
       </c>
       <c r="F360" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr">
@@ -16468,7 +16468,7 @@
       </c>
       <c r="F361" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G361" s="3" t="inlineStr">
@@ -16510,7 +16510,7 @@
       </c>
       <c r="F362" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G362" s="3" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="F363" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G363" s="4" t="inlineStr">
@@ -16614,7 +16614,7 @@
       </c>
       <c r="F364" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G364" s="3" t="inlineStr">
@@ -16658,7 +16658,7 @@
       </c>
       <c r="F365" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G365" s="3" t="inlineStr">
@@ -16708,7 +16708,7 @@
       </c>
       <c r="F366" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G366" s="3" t="inlineStr">
@@ -16748,7 +16748,7 @@
       </c>
       <c r="F367" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G367" s="3" t="inlineStr">
@@ -16792,7 +16792,7 @@
       </c>
       <c r="F368" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G368" s="3" t="inlineStr">
@@ -16832,7 +16832,7 @@
       </c>
       <c r="F369" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G369" s="3" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="F370" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G370" s="3" t="inlineStr">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="F371" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G371" s="3" t="inlineStr">
@@ -16956,7 +16956,7 @@
       </c>
       <c r="F372" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G372" s="3" t="inlineStr">
@@ -16996,7 +16996,7 @@
       </c>
       <c r="F373" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G373" s="3" t="inlineStr">
@@ -17036,7 +17036,7 @@
       </c>
       <c r="F374" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G374" s="3" t="inlineStr">
@@ -17078,7 +17078,7 @@
       </c>
       <c r="F375" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G375" s="3" t="inlineStr">
@@ -17130,7 +17130,7 @@
       </c>
       <c r="F376" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G376" s="3" t="inlineStr">
@@ -17170,7 +17170,7 @@
       </c>
       <c r="F377" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G377" s="3" t="inlineStr">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="F378" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G378" s="3" t="inlineStr">
@@ -17254,7 +17254,7 @@
       </c>
       <c r="F379" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G379" s="3" t="inlineStr">
@@ -17296,7 +17296,7 @@
       </c>
       <c r="F380" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G380" s="3" t="inlineStr">
@@ -17338,7 +17338,7 @@
       </c>
       <c r="F381" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G381" s="3" t="inlineStr">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="F382" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G382" s="3" t="inlineStr">
@@ -17422,7 +17422,7 @@
       </c>
       <c r="F383" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G383" s="3" t="inlineStr">
@@ -17472,7 +17472,7 @@
       </c>
       <c r="F384" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G384" s="3" t="inlineStr">
@@ -17512,7 +17512,7 @@
       </c>
       <c r="F385" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G385" s="3" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="F386" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G386" s="3" t="inlineStr">
@@ -17594,7 +17594,7 @@
       </c>
       <c r="F387" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G387" s="3" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="F388" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G388" s="4" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="F389" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G389" s="4" t="inlineStr">
@@ -17716,7 +17716,7 @@
       </c>
       <c r="F390" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G390" s="4" t="inlineStr">
@@ -17756,7 +17756,7 @@
       </c>
       <c r="F391" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G391" s="3" t="inlineStr">
@@ -17798,7 +17798,7 @@
       </c>
       <c r="F392" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G392" s="3" t="inlineStr">
@@ -17840,7 +17840,7 @@
       </c>
       <c r="F393" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G393" s="3" t="inlineStr">
@@ -17882,7 +17882,7 @@
       </c>
       <c r="F394" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G394" s="3" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="F395" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G395" s="3" t="inlineStr">
@@ -17976,7 +17976,7 @@
       </c>
       <c r="F396" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G396" s="3" t="inlineStr">
@@ -18018,7 +18018,7 @@
       </c>
       <c r="F397" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G397" s="3" t="inlineStr">
@@ -18062,7 +18062,7 @@
       </c>
       <c r="F398" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G398" s="3" t="inlineStr">
@@ -18104,7 +18104,7 @@
       </c>
       <c r="F399" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G399" s="3" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="F400" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G400" s="3" t="inlineStr">
@@ -18184,7 +18184,7 @@
       </c>
       <c r="F401" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G401" s="3" t="inlineStr">
@@ -18224,7 +18224,7 @@
       </c>
       <c r="F402" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G402" s="3" t="inlineStr">
@@ -18264,7 +18264,7 @@
       </c>
       <c r="F403" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G403" s="3" t="inlineStr">
@@ -18304,7 +18304,7 @@
       </c>
       <c r="F404" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G404" s="3" t="inlineStr">
@@ -18344,7 +18344,7 @@
       </c>
       <c r="F405" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G405" s="3" t="inlineStr">
@@ -18384,7 +18384,7 @@
       </c>
       <c r="F406" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G406" s="3" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="F407" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G407" s="3" t="inlineStr">
@@ -18464,7 +18464,7 @@
       </c>
       <c r="F408" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G408" s="3" t="inlineStr">
@@ -18504,7 +18504,7 @@
       </c>
       <c r="F409" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G409" s="3" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="F410" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G410" s="3" t="inlineStr">
@@ -18584,7 +18584,7 @@
       </c>
       <c r="F411" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G411" s="3" t="inlineStr">
@@ -18626,7 +18626,7 @@
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G412" s="3" t="inlineStr">
@@ -18668,7 +18668,7 @@
       </c>
       <c r="F413" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G413" s="3" t="inlineStr">
@@ -18710,7 +18710,7 @@
       </c>
       <c r="F414" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G414" s="3" t="inlineStr">
@@ -18752,7 +18752,7 @@
       </c>
       <c r="F415" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G415" s="3" t="inlineStr">
@@ -18794,7 +18794,7 @@
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G416" s="3" t="inlineStr">
@@ -18836,7 +18836,7 @@
       </c>
       <c r="F417" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G417" s="3" t="inlineStr">
@@ -18878,7 +18878,7 @@
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G418" s="3" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G419" s="3" t="inlineStr">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="F420" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G420" s="3" t="inlineStr">
@@ -19002,7 +19002,7 @@
       </c>
       <c r="F421" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G421" s="3" t="inlineStr">
@@ -19042,7 +19042,7 @@
       </c>
       <c r="F422" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G422" s="3" t="inlineStr">
@@ -19082,7 +19082,7 @@
       </c>
       <c r="F423" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G423" s="3" t="inlineStr">
@@ -19122,7 +19122,7 @@
       </c>
       <c r="F424" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G424" s="3" t="inlineStr">
@@ -19164,7 +19164,7 @@
       </c>
       <c r="F425" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G425" s="3" t="inlineStr">
@@ -19206,7 +19206,7 @@
       </c>
       <c r="F426" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G426" s="3" t="inlineStr">
@@ -19248,7 +19248,7 @@
       </c>
       <c r="F427" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G427" s="3" t="inlineStr">
@@ -19290,7 +19290,7 @@
       </c>
       <c r="F428" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G428" s="3" t="inlineStr">
@@ -19332,7 +19332,7 @@
       </c>
       <c r="F429" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G429" s="3" t="inlineStr">
@@ -19374,7 +19374,7 @@
       </c>
       <c r="F430" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G430" s="3" t="inlineStr">
@@ -19416,7 +19416,7 @@
       </c>
       <c r="F431" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G431" s="3" t="inlineStr">
@@ -19458,7 +19458,7 @@
       </c>
       <c r="F432" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G432" s="3" t="inlineStr">
@@ -19500,7 +19500,7 @@
       </c>
       <c r="F433" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G433" s="3" t="inlineStr">
@@ -19542,7 +19542,7 @@
       </c>
       <c r="F434" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G434" s="3" t="inlineStr">
@@ -19584,7 +19584,7 @@
       </c>
       <c r="F435" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G435" s="3" t="inlineStr">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="F436" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G436" s="3" t="inlineStr">
@@ -19668,7 +19668,7 @@
       </c>
       <c r="F437" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G437" s="3" t="inlineStr">
@@ -19710,7 +19710,7 @@
       </c>
       <c r="F438" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G438" s="3" t="inlineStr">
@@ -19752,7 +19752,7 @@
       </c>
       <c r="F439" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G439" s="3" t="inlineStr">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G440" s="3" t="inlineStr">
@@ -19836,7 +19836,7 @@
       </c>
       <c r="F441" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G441" s="3" t="inlineStr">
@@ -19878,7 +19878,7 @@
       </c>
       <c r="F442" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G442" s="3" t="inlineStr">
@@ -19920,7 +19920,7 @@
       </c>
       <c r="F443" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G443" s="3" t="inlineStr">
@@ -19962,7 +19962,7 @@
       </c>
       <c r="F444" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G444" s="3" t="inlineStr">
@@ -20004,7 +20004,7 @@
       </c>
       <c r="F445" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G445" s="3" t="inlineStr">
@@ -20046,7 +20046,7 @@
       </c>
       <c r="F446" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G446" s="3" t="inlineStr">
@@ -20088,7 +20088,7 @@
       </c>
       <c r="F447" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G447" s="3" t="inlineStr">
@@ -20130,7 +20130,7 @@
       </c>
       <c r="F448" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G448" s="3" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="F449" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G449" s="3" t="inlineStr">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="F450" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G450" s="3" t="inlineStr">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="F451" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G451" s="3" t="inlineStr">
@@ -20300,7 +20300,7 @@
       </c>
       <c r="F452" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G452" s="3" t="inlineStr">
@@ -20342,7 +20342,7 @@
       </c>
       <c r="F453" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G453" s="3" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="F454" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G454" s="3" t="inlineStr">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="F455" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G455" s="3" t="inlineStr">
@@ -20468,7 +20468,7 @@
       </c>
       <c r="F456" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G456" s="3" t="inlineStr">
@@ -20510,7 +20510,7 @@
       </c>
       <c r="F457" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G457" s="3" t="inlineStr">
@@ -20550,7 +20550,7 @@
       </c>
       <c r="F458" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G458" s="3" t="inlineStr">
@@ -20590,7 +20590,7 @@
       </c>
       <c r="F459" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G459" s="3" t="inlineStr">
@@ -20630,7 +20630,7 @@
       </c>
       <c r="F460" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G460" s="3" t="inlineStr">
@@ -20670,7 +20670,7 @@
       </c>
       <c r="F461" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G461" s="3" t="inlineStr">
@@ -20714,7 +20714,7 @@
       </c>
       <c r="F462" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G462" s="3" t="inlineStr">
@@ -20788,7 +20788,7 @@
       </c>
       <c r="F463" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G463" s="3" t="inlineStr">
@@ -20830,7 +20830,7 @@
       </c>
       <c r="F464" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G464" s="3" t="inlineStr">
@@ -20872,7 +20872,7 @@
       </c>
       <c r="F465" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G465" s="3" t="inlineStr">
@@ -20928,7 +20928,7 @@
       </c>
       <c r="F466" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G466" s="3" t="inlineStr">
@@ -20970,7 +20970,7 @@
       </c>
       <c r="F467" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G467" s="3" t="inlineStr">
@@ -21012,7 +21012,7 @@
       </c>
       <c r="F468" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G468" s="3" t="inlineStr">
@@ -21054,7 +21054,7 @@
       </c>
       <c r="F469" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G469" s="3" t="inlineStr">
@@ -21094,7 +21094,7 @@
       </c>
       <c r="F470" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G470" s="3" t="inlineStr">
@@ -21134,7 +21134,7 @@
       </c>
       <c r="F471" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G471" s="3" t="inlineStr">
@@ -21174,7 +21174,7 @@
       </c>
       <c r="F472" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G472" s="3" t="inlineStr">
@@ -21214,7 +21214,7 @@
       </c>
       <c r="F473" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G473" s="3" t="inlineStr">
@@ -21254,7 +21254,7 @@
       </c>
       <c r="F474" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G474" s="3" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="F475" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G475" s="3" t="inlineStr">
@@ -21334,7 +21334,7 @@
       </c>
       <c r="F476" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G476" s="3" t="inlineStr">
@@ -21374,7 +21374,7 @@
       </c>
       <c r="F477" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G477" s="3" t="inlineStr">
@@ -21414,7 +21414,7 @@
       </c>
       <c r="F478" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G478" s="3" t="inlineStr">
@@ -21454,7 +21454,7 @@
       </c>
       <c r="F479" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G479" s="3" t="inlineStr">
@@ -21494,7 +21494,7 @@
       </c>
       <c r="F480" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G480" s="3" t="inlineStr">
@@ -21534,7 +21534,7 @@
       </c>
       <c r="F481" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G481" s="3" t="inlineStr">
@@ -21576,7 +21576,7 @@
       </c>
       <c r="F482" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G482" s="3" t="inlineStr">
@@ -21618,7 +21618,7 @@
       </c>
       <c r="F483" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G483" s="3" t="inlineStr">
@@ -21658,7 +21658,7 @@
       </c>
       <c r="F484" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G484" s="3" t="inlineStr">
@@ -21698,7 +21698,7 @@
       </c>
       <c r="F485" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G485" s="3" t="inlineStr">
@@ -21738,7 +21738,7 @@
       </c>
       <c r="F486" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G486" s="3" t="inlineStr">
@@ -21778,7 +21778,7 @@
       </c>
       <c r="F487" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G487" s="3" t="inlineStr">
@@ -21820,7 +21820,7 @@
       </c>
       <c r="F488" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G488" s="3" t="inlineStr">
@@ -21862,7 +21862,7 @@
       </c>
       <c r="F489" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G489" s="3" t="inlineStr">
@@ -21904,7 +21904,7 @@
       </c>
       <c r="F490" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G490" s="3" t="inlineStr">
@@ -21946,7 +21946,7 @@
       </c>
       <c r="F491" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G491" s="3" t="inlineStr">
@@ -21986,7 +21986,7 @@
       </c>
       <c r="F492" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G492" s="3" t="inlineStr">
@@ -22028,7 +22028,7 @@
       </c>
       <c r="F493" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G493" s="3" t="inlineStr">
@@ -22070,7 +22070,7 @@
       </c>
       <c r="F494" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G494" s="3" t="inlineStr">
@@ -22120,7 +22120,7 @@
       </c>
       <c r="F495" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G495" s="3" t="inlineStr">
@@ -22160,7 +22160,7 @@
       </c>
       <c r="F496" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G496" s="3" t="inlineStr">
@@ -22200,7 +22200,7 @@
       </c>
       <c r="F497" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G497" s="3" t="inlineStr">
@@ -22240,7 +22240,7 @@
       </c>
       <c r="F498" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G498" s="3" t="inlineStr">
@@ -22280,7 +22280,7 @@
       </c>
       <c r="F499" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G499" s="3" t="inlineStr">
@@ -22320,7 +22320,7 @@
       </c>
       <c r="F500" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G500" s="3" t="inlineStr">
@@ -22360,7 +22360,7 @@
       </c>
       <c r="F501" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G501" s="3" t="inlineStr">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="F502" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G502" s="3" t="inlineStr">
@@ -22440,7 +22440,7 @@
       </c>
       <c r="F503" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G503" s="3" t="inlineStr">
@@ -22480,7 +22480,7 @@
       </c>
       <c r="F504" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G504" s="3" t="inlineStr">
@@ -22520,7 +22520,7 @@
       </c>
       <c r="F505" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G505" s="3" t="inlineStr">
@@ -22560,7 +22560,7 @@
       </c>
       <c r="F506" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G506" s="3" t="inlineStr">
@@ -22600,7 +22600,7 @@
       </c>
       <c r="F507" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G507" s="3" t="inlineStr">
@@ -22640,7 +22640,7 @@
       </c>
       <c r="F508" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G508" s="3" t="inlineStr">
@@ -22680,7 +22680,7 @@
       </c>
       <c r="F509" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G509" s="3" t="inlineStr">
@@ -22720,7 +22720,7 @@
       </c>
       <c r="F510" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G510" s="3" t="inlineStr">
@@ -22760,7 +22760,7 @@
       </c>
       <c r="F511" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G511" s="3" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="F512" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G512" s="3" t="inlineStr">
@@ -22854,7 +22854,7 @@
       </c>
       <c r="F513" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G513" s="3" t="inlineStr">
@@ -22894,7 +22894,7 @@
       </c>
       <c r="F514" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G514" s="3" t="inlineStr">
@@ -22934,7 +22934,7 @@
       </c>
       <c r="F515" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G515" s="3" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="F516" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G516" s="3" t="inlineStr">
@@ -23016,7 +23016,7 @@
       </c>
       <c r="F517" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G517" s="3" t="inlineStr">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="F518" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G518" s="3" t="inlineStr">
@@ -23098,7 +23098,7 @@
       </c>
       <c r="F519" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G519" s="3" t="inlineStr">
@@ -23140,7 +23140,7 @@
       </c>
       <c r="F520" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G520" s="3" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="F521" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G521" s="3" t="inlineStr">
@@ -23220,7 +23220,7 @@
       </c>
       <c r="F522" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G522" s="3" t="inlineStr">
@@ -23260,7 +23260,7 @@
       </c>
       <c r="F523" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G523" s="3" t="inlineStr">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="F524" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G524" s="3" t="inlineStr">
@@ -23350,7 +23350,7 @@
       </c>
       <c r="F525" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G525" s="3" t="inlineStr">
@@ -23392,7 +23392,7 @@
       </c>
       <c r="F526" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G526" s="3" t="inlineStr">
@@ -23438,7 +23438,7 @@
       </c>
       <c r="F527" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G527" s="3" t="inlineStr">
@@ -23478,7 +23478,7 @@
       </c>
       <c r="F528" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G528" s="3" t="inlineStr">
@@ -23520,7 +23520,7 @@
       </c>
       <c r="F529" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G529" s="3" t="inlineStr">
@@ -23562,7 +23562,7 @@
       </c>
       <c r="F530" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G530" s="3" t="inlineStr">
@@ -23614,7 +23614,7 @@
       </c>
       <c r="F531" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G531" s="3" t="inlineStr">
@@ -23656,7 +23656,7 @@
       </c>
       <c r="F532" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G532" s="3" t="inlineStr">
@@ -23777,7 +23777,7 @@
       </c>
       <c r="F533" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G533" s="3" t="inlineStr">
@@ -23819,7 +23819,7 @@
       </c>
       <c r="F534" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G534" s="3" t="inlineStr">
@@ -23859,7 +23859,7 @@
       </c>
       <c r="F535" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G535" s="3" t="inlineStr">
@@ -23899,7 +23899,7 @@
       </c>
       <c r="F536" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G536" s="3" t="inlineStr">
@@ -23939,7 +23939,7 @@
       </c>
       <c r="F537" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G537" s="3" t="inlineStr">
@@ -23979,7 +23979,7 @@
       </c>
       <c r="F538" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G538" s="3" t="inlineStr">
@@ -24019,7 +24019,7 @@
       </c>
       <c r="F539" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G539" s="3" t="inlineStr">
@@ -24059,7 +24059,7 @@
       </c>
       <c r="F540" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G540" s="3" t="inlineStr">
@@ -24100,7 +24100,7 @@
       </c>
       <c r="F541" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G541" s="3" t="inlineStr">
@@ -24142,7 +24142,7 @@
       </c>
       <c r="F542" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G542" s="3" t="inlineStr">
@@ -24184,7 +24184,7 @@
       </c>
       <c r="F543" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G543" s="3" t="inlineStr">
@@ -24236,7 +24236,7 @@
       </c>
       <c r="F544" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G544" s="3" t="inlineStr">
@@ -24280,7 +24280,7 @@
       </c>
       <c r="F545" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G545" s="3" t="inlineStr">
@@ -24322,7 +24322,7 @@
       </c>
       <c r="F546" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G546" s="3" t="inlineStr">
@@ -24362,7 +24362,7 @@
       </c>
       <c r="F547" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G547" s="3" t="inlineStr">
@@ -24404,7 +24404,7 @@
       </c>
       <c r="F548" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G548" s="3" t="inlineStr">
@@ -24448,7 +24448,7 @@
       </c>
       <c r="F549" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G549" s="3" t="inlineStr">
@@ -24490,7 +24490,7 @@
       </c>
       <c r="F550" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G550" s="3" t="inlineStr">
@@ -24530,7 +24530,7 @@
       </c>
       <c r="F551" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G551" s="3" t="inlineStr">
@@ -24570,7 +24570,7 @@
       </c>
       <c r="F552" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G552" s="3" t="inlineStr">
@@ -24612,7 +24612,7 @@
       </c>
       <c r="F553" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G553" s="3" t="inlineStr">
@@ -24660,7 +24660,7 @@
       </c>
       <c r="F554" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G554" s="3" t="inlineStr">
@@ -24702,7 +24702,7 @@
       </c>
       <c r="F555" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G555" s="3" t="inlineStr">
@@ -24744,7 +24744,7 @@
       </c>
       <c r="F556" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G556" s="3" t="inlineStr">
@@ -24790,7 +24790,7 @@
       </c>
       <c r="F557" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G557" s="3" t="inlineStr">
@@ -24830,7 +24830,7 @@
       </c>
       <c r="F558" s="2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>zh-Hans</t>
         </is>
       </c>
       <c r="G558" s="3" t="inlineStr">
